--- a/artfynd/A 29392-2025 artfynd.xlsx
+++ b/artfynd/A 29392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126811501</v>
       </c>
       <c r="B2" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126805764</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29392-2025 artfynd.xlsx
+++ b/artfynd/A 29392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126811501</v>
       </c>
       <c r="B2" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126805764</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29392-2025 artfynd.xlsx
+++ b/artfynd/A 29392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126811501</v>
       </c>
       <c r="B2" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29392-2025 artfynd.xlsx
+++ b/artfynd/A 29392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126811501</v>
       </c>
       <c r="B2" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126805968</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126805764</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29392-2025 artfynd.xlsx
+++ b/artfynd/A 29392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126811501</v>
       </c>
       <c r="B2" t="n">
-        <v>97331</v>
+        <v>97320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126805968</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126805764</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29392-2025 artfynd.xlsx
+++ b/artfynd/A 29392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126811501</v>
       </c>
       <c r="B2" t="n">
-        <v>97320</v>
+        <v>97331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126805968</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126805764</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
